--- a/jogos_2025-04-09.xlsx
+++ b/jogos_2025-04-09.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="208">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -250,18 +196,18 @@
     <t>Georgia Erovnuli Liga</t>
   </si>
   <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Slovenia PrvaLiga</t>
   </si>
   <si>
-    <t>Estonia Meistriliiga</t>
+    <t>Poland 1. Liga</t>
   </si>
   <si>
     <t>Czech Republic First League</t>
   </si>
   <si>
-    <t>Poland 1. Liga</t>
-  </si>
-  <si>
     <t>Italy Serie C Group B</t>
   </si>
   <si>
@@ -310,54 +256,54 @@
     <t>Erokspor</t>
   </si>
   <si>
+    <t>Nõmme Kalju</t>
+  </si>
+  <si>
+    <t>Olimpija</t>
+  </si>
+  <si>
     <t>Samgurali</t>
   </si>
   <si>
-    <t>Olimpija</t>
-  </si>
-  <si>
-    <t>Nõmme Kalju</t>
+    <t>Paide</t>
+  </si>
+  <si>
+    <t>Wisła Kraków</t>
+  </si>
+  <si>
+    <t>Dinamo Tbilisi</t>
   </si>
   <si>
     <t>Slovácko</t>
   </si>
   <si>
-    <t>Wisła Kraków</t>
-  </si>
-  <si>
-    <t>Paide</t>
-  </si>
-  <si>
     <t>Pescara</t>
   </si>
   <si>
-    <t>Dinamo Tbilisi</t>
+    <t>Energie Cottbus</t>
+  </si>
+  <si>
+    <t>Verl</t>
   </si>
   <si>
     <t>1860 München</t>
   </si>
   <si>
-    <t>Verl</t>
+    <t>Osnabrück</t>
   </si>
   <si>
     <t>Fredrikstad</t>
   </si>
   <si>
+    <t>Boluspor</t>
+  </si>
+  <si>
     <t>Dynamo Dresden</t>
   </si>
   <si>
-    <t>Energie Cottbus</t>
-  </si>
-  <si>
-    <t>Osnabrück</t>
-  </si>
-  <si>
     <t>Pendikspor</t>
   </si>
   <si>
-    <t>Boluspor</t>
-  </si>
-  <si>
     <t>Polonia Warszawa</t>
   </si>
   <si>
@@ -370,15 +316,15 @@
     <t>Swansea City</t>
   </si>
   <si>
+    <t>FC Barcelona</t>
+  </si>
+  <si>
+    <t>PSG</t>
+  </si>
+  <si>
     <t>Coventry City</t>
   </si>
   <si>
-    <t>PSG</t>
-  </si>
-  <si>
-    <t>FC Barcelona</t>
-  </si>
-  <si>
     <t>Cavalier</t>
   </si>
   <si>
@@ -400,12 +346,12 @@
     <t>Flamengo</t>
   </si>
   <si>
+    <t>Bolívar</t>
+  </si>
+  <si>
     <t>Palmeiras</t>
   </si>
   <si>
-    <t>Bolívar</t>
-  </si>
-  <si>
     <t>LDU Quito</t>
   </si>
   <si>
@@ -427,54 +373,54 @@
     <t>Fatih Karagümrük</t>
   </si>
   <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
+    <t>Koper</t>
+  </si>
+  <si>
     <t>Dila</t>
   </si>
   <si>
-    <t>Koper</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
+    <t>Vaprus</t>
+  </si>
+  <si>
+    <t>Chrobry Głogów</t>
+  </si>
+  <si>
+    <t>Saburtalo</t>
   </si>
   <si>
     <t>Hradec Králové</t>
   </si>
   <si>
-    <t>Chrobry Głogów</t>
-  </si>
-  <si>
-    <t>Vaprus</t>
-  </si>
-  <si>
     <t>Arezzo</t>
   </si>
   <si>
-    <t>Saburtalo</t>
+    <t>Rot-Weiss Essen</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund II</t>
   </si>
   <si>
     <t>Sandhausen</t>
   </si>
   <si>
-    <t>Borussia Dortmund II</t>
+    <t>Hansa Rostock</t>
   </si>
   <si>
     <t>Vålerenga</t>
   </si>
   <si>
+    <t>Sakaryaspor</t>
+  </si>
+  <si>
     <t>Ingolstadt</t>
   </si>
   <si>
-    <t>Rot-Weiss Essen</t>
-  </si>
-  <si>
-    <t>Hansa Rostock</t>
-  </si>
-  <si>
     <t>Ankaragücü</t>
   </si>
   <si>
-    <t>Sakaryaspor</t>
-  </si>
-  <si>
     <t>Pogoń Siedlce</t>
   </si>
   <si>
@@ -487,15 +433,15 @@
     <t>Plymouth Argyle</t>
   </si>
   <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>Aston Villa</t>
+  </si>
+  <si>
     <t>Portsmouth</t>
   </si>
   <si>
-    <t>Aston Villa</t>
-  </si>
-  <si>
-    <t>Borussia Dortmund</t>
-  </si>
-  <si>
     <t>Portmore United</t>
   </si>
   <si>
@@ -517,12 +463,12 @@
     <t>Central Córdoba SdE</t>
   </si>
   <si>
+    <t>Sporting Cristal</t>
+  </si>
+  <si>
     <t>Cerro Porteño</t>
   </si>
   <si>
-    <t>Sporting Cristal</t>
-  </si>
-  <si>
     <t>Deportivo Táchira</t>
   </si>
   <si>
@@ -547,18 +493,18 @@
     <t>['24', '45+5']</t>
   </si>
   <si>
+    <t>['4', '9', '16']</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
-    <t>['4', '9', '16']</t>
+    <t>['5']</t>
   </si>
   <si>
     <t>['24', '62']</t>
   </si>
   <si>
-    <t>['5']</t>
-  </si>
-  <si>
     <t>['86']</t>
   </si>
   <si>
@@ -568,30 +514,30 @@
     <t>['39', '76']</t>
   </si>
   <si>
+    <t>['12', '23', '90+1']</t>
+  </si>
+  <si>
     <t>['42', '73']</t>
   </si>
   <si>
     <t>['18', '35']</t>
   </si>
   <si>
-    <t>['12', '23', '90+1']</t>
-  </si>
-  <si>
     <t>['7', '36']</t>
   </si>
   <si>
     <t>['4', '22', '35']</t>
   </si>
   <si>
+    <t>['25', '48', '66', '77']</t>
+  </si>
+  <si>
+    <t>['39', '49', '90+2']</t>
+  </si>
+  <si>
     <t>['90+4']</t>
   </si>
   <si>
-    <t>['39', '49', '90+2']</t>
-  </si>
-  <si>
-    <t>['25', '48', '66', '77']</t>
-  </si>
-  <si>
     <t>['56']</t>
   </si>
   <si>
@@ -607,12 +553,12 @@
     <t>['60']</t>
   </si>
   <si>
+    <t>['12', '44', '58']</t>
+  </si>
+  <si>
     <t>['41']</t>
   </si>
   <si>
-    <t>['12', '44', '58']</t>
-  </si>
-  <si>
     <t>['73', '83']</t>
   </si>
   <si>
@@ -634,37 +580,37 @@
     <t>['37']</t>
   </si>
   <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>['52']</t>
   </si>
   <si>
-    <t>['79']</t>
+    <t>['6']</t>
+  </si>
+  <si>
+    <t>['33', '41']</t>
   </si>
   <si>
     <t>['17', '24', '30', '84', '90+4']</t>
   </si>
   <si>
-    <t>['6']</t>
-  </si>
-  <si>
     <t>['90+3']</t>
   </si>
   <si>
-    <t>['33', '41']</t>
+    <t>['3']</t>
+  </si>
+  <si>
+    <t>['50']</t>
+  </si>
+  <si>
+    <t>['53']</t>
   </si>
   <si>
     <t>['35', '48']</t>
   </si>
   <si>
-    <t>['3']</t>
-  </si>
-  <si>
-    <t>['50']</t>
-  </si>
-  <si>
     <t>['13']</t>
-  </si>
-  <si>
-    <t>['53']</t>
   </si>
   <si>
     <t>['80']</t>
@@ -1055,10 +1001,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD40"/>
+  <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,79 +1119,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45756</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="G2">
         <v>1</v>
@@ -1260,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L2">
         <v>1.66</v>
@@ -1335,87 +1227,33 @@
         <v>1.42</v>
       </c>
       <c r="AJ2" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="AK2" t="s">
-        <v>200</v>
-      </c>
-      <c r="AL2">
-        <v>1.29</v>
-      </c>
-      <c r="AM2">
-        <v>1.2</v>
-      </c>
-      <c r="AN2">
-        <v>2.01</v>
-      </c>
-      <c r="AO2">
-        <v>14</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>1.95</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.44</v>
-      </c>
-      <c r="BC2">
-        <v>2.75</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>182</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45756.29166666666</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45756</v>
       </c>
       <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
         <v>56</v>
       </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="G3">
         <v>3</v>
@@ -1430,7 +1268,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L3">
         <v>1.62</v>
@@ -1505,87 +1343,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ3" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="AK3" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL3">
-        <v>1.18</v>
-      </c>
-      <c r="AM3">
-        <v>1.18</v>
-      </c>
-      <c r="AN3">
-        <v>2.15</v>
-      </c>
-      <c r="AO3">
-        <v>13</v>
-      </c>
-      <c r="AP3">
-        <v>1.26</v>
-      </c>
-      <c r="AQ3">
-        <v>1.46</v>
-      </c>
-      <c r="AR3">
-        <v>1.78</v>
-      </c>
-      <c r="AS3">
-        <v>2.23</v>
-      </c>
-      <c r="AT3">
-        <v>2.8</v>
-      </c>
-      <c r="AU3">
-        <v>3.25</v>
-      </c>
-      <c r="AV3">
-        <v>2.4</v>
-      </c>
-      <c r="AW3">
-        <v>1.87</v>
-      </c>
-      <c r="AX3">
-        <v>1.54</v>
-      </c>
-      <c r="AY3">
-        <v>1.35</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>1.55</v>
-      </c>
-      <c r="BC3">
-        <v>2.7</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>183</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45756.29166666666</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45756</v>
       </c>
       <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1600,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L4">
         <v>1.98</v>
@@ -1675,87 +1459,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ4" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="AK4" t="s">
-        <v>202</v>
-      </c>
-      <c r="AL4">
-        <v>1.25</v>
-      </c>
-      <c r="AM4">
-        <v>1.28</v>
-      </c>
-      <c r="AN4">
-        <v>1.77</v>
-      </c>
-      <c r="AO4">
-        <v>9</v>
-      </c>
-      <c r="AP4">
-        <v>1.45</v>
-      </c>
-      <c r="AQ4">
-        <v>1.75</v>
-      </c>
-      <c r="AR4">
-        <v>2.2</v>
-      </c>
-      <c r="AS4">
-        <v>2.88</v>
-      </c>
-      <c r="AT4">
-        <v>3.8</v>
-      </c>
-      <c r="AU4">
-        <v>2.55</v>
-      </c>
-      <c r="AV4">
-        <v>1.95</v>
-      </c>
-      <c r="AW4">
-        <v>1.58</v>
-      </c>
-      <c r="AX4">
-        <v>1.35</v>
-      </c>
-      <c r="AY4">
-        <v>1.22</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.62</v>
-      </c>
-      <c r="BC4">
-        <v>2.63</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>184</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45756.3125</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45756</v>
       </c>
       <c r="B5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -1770,7 +1500,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L5">
         <v>2.12</v>
@@ -1845,87 +1575,33 @@
         <v>1.02</v>
       </c>
       <c r="AJ5" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK5" t="s">
-        <v>203</v>
-      </c>
-      <c r="AL5">
-        <v>1.29</v>
-      </c>
-      <c r="AM5">
-        <v>1.36</v>
-      </c>
-      <c r="AN5">
-        <v>1.7</v>
-      </c>
-      <c r="AO5">
-        <v>8</v>
-      </c>
-      <c r="AP5">
-        <v>1.48</v>
-      </c>
-      <c r="AQ5">
-        <v>1.87</v>
-      </c>
-      <c r="AR5">
-        <v>2.46</v>
-      </c>
-      <c r="AS5">
-        <v>3.42</v>
-      </c>
-      <c r="AT5">
-        <v>4.33</v>
-      </c>
-      <c r="AU5">
-        <v>2.33</v>
-      </c>
-      <c r="AV5">
-        <v>1.79</v>
-      </c>
-      <c r="AW5">
-        <v>1.43</v>
-      </c>
-      <c r="AX5">
-        <v>1.23</v>
-      </c>
-      <c r="AY5">
-        <v>1.18</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>1.67</v>
-      </c>
-      <c r="BC5">
-        <v>2.63</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>185</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45756.33333333334</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45756</v>
       </c>
       <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" t="s">
         <v>59</v>
       </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1940,7 +1616,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L6">
         <v>3.1</v>
@@ -2015,87 +1691,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ6" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="AK6" t="s">
-        <v>204</v>
-      </c>
-      <c r="AL6">
-        <v>1.99</v>
-      </c>
-      <c r="AM6">
-        <v>1.32</v>
-      </c>
-      <c r="AN6">
-        <v>1.2</v>
-      </c>
-      <c r="AO6">
-        <v>10</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>2.75</v>
-      </c>
-      <c r="BC6">
-        <v>1.57</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>186</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45756.41666666666</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45756</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -2110,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L7">
         <v>2.7</v>
@@ -2185,257 +1807,149 @@
         <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="AK7" t="s">
-        <v>205</v>
-      </c>
-      <c r="AL7">
-        <v>1.5</v>
-      </c>
-      <c r="AM7">
-        <v>1.33</v>
-      </c>
-      <c r="AN7">
-        <v>1.44</v>
-      </c>
-      <c r="AO7">
-        <v>10</v>
-      </c>
-      <c r="AP7">
-        <v>1.41</v>
-      </c>
-      <c r="AQ7">
-        <v>1.76</v>
-      </c>
-      <c r="AR7">
-        <v>2.26</v>
-      </c>
-      <c r="AS7">
-        <v>3.08</v>
-      </c>
-      <c r="AT7">
-        <v>4.05</v>
-      </c>
-      <c r="AU7">
-        <v>2.52</v>
-      </c>
-      <c r="AV7">
-        <v>1.91</v>
-      </c>
-      <c r="AW7">
-        <v>1.51</v>
-      </c>
-      <c r="AX7">
-        <v>1.28</v>
-      </c>
-      <c r="AY7">
-        <v>1.18</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>2.1</v>
-      </c>
-      <c r="BC7">
-        <v>1.83</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>187</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45756.45833333334</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45756</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F8" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L8">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="M8">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N8">
-        <v>1.95</v>
+        <v>6</v>
       </c>
       <c r="O8">
-        <v>2.75</v>
+        <v>1.3</v>
       </c>
       <c r="P8">
-        <v>7.8</v>
+        <v>15</v>
       </c>
       <c r="Q8">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="R8">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="S8">
+        <v>3.8</v>
+      </c>
+      <c r="T8">
+        <v>2.1</v>
+      </c>
+      <c r="U8">
+        <v>1.7</v>
+      </c>
+      <c r="V8">
+        <v>4.33</v>
+      </c>
+      <c r="W8">
+        <v>1.18</v>
+      </c>
+      <c r="X8">
+        <v>1.02</v>
+      </c>
+      <c r="Y8">
+        <v>10</v>
+      </c>
+      <c r="Z8">
+        <v>1.09</v>
+      </c>
+      <c r="AA8">
+        <v>6.25</v>
+      </c>
+      <c r="AB8">
+        <v>1.42</v>
+      </c>
+      <c r="AC8">
         <v>2.62</v>
       </c>
-      <c r="T8">
-        <v>3</v>
-      </c>
-      <c r="U8">
-        <v>1.36</v>
-      </c>
-      <c r="V8">
-        <v>7.5</v>
-      </c>
-      <c r="W8">
-        <v>1.07</v>
-      </c>
-      <c r="X8">
-        <v>1.07</v>
-      </c>
-      <c r="Y8">
-        <v>8</v>
-      </c>
-      <c r="Z8">
-        <v>1.37</v>
-      </c>
-      <c r="AA8">
-        <v>2.66</v>
-      </c>
-      <c r="AB8">
+      <c r="AD8">
         <v>2.15</v>
       </c>
-      <c r="AC8">
-        <v>1.57</v>
-      </c>
-      <c r="AD8">
-        <v>4.15</v>
-      </c>
       <c r="AE8">
-        <v>1.16</v>
+        <v>1.69</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AG8">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AH8">
-        <v>8.5</v>
+        <v>3.55</v>
       </c>
       <c r="AI8">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AJ8" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="AK8" t="s">
-        <v>206</v>
-      </c>
-      <c r="AL8">
-        <v>1.8</v>
-      </c>
-      <c r="AM8">
-        <v>1.33</v>
-      </c>
-      <c r="AN8">
-        <v>1.2</v>
-      </c>
-      <c r="AO8">
-        <v>8</v>
-      </c>
-      <c r="AP8">
-        <v>0</v>
-      </c>
-      <c r="AQ8">
-        <v>0</v>
-      </c>
-      <c r="AR8">
-        <v>0</v>
-      </c>
-      <c r="AS8">
-        <v>0</v>
-      </c>
-      <c r="AT8">
-        <v>0</v>
-      </c>
-      <c r="AU8">
-        <v>0</v>
-      </c>
-      <c r="AV8">
-        <v>0</v>
-      </c>
-      <c r="AW8">
-        <v>0</v>
-      </c>
-      <c r="AX8">
-        <v>0</v>
-      </c>
-      <c r="AY8">
-        <v>0</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>2.75</v>
-      </c>
-      <c r="BC8">
-        <v>1.57</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45756.5</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45756</v>
       </c>
       <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
         <v>61</v>
       </c>
-      <c r="C9" t="s">
-        <v>78</v>
-      </c>
       <c r="D9" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F9" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -2450,7 +1964,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L9">
         <v>1.51</v>
@@ -2525,427 +2039,265 @@
         <v>1.06</v>
       </c>
       <c r="AJ9" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK9" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL9">
-        <v>1.09</v>
-      </c>
-      <c r="AM9">
-        <v>1.18</v>
-      </c>
-      <c r="AN9">
-        <v>2.45</v>
-      </c>
-      <c r="AO9">
-        <v>10</v>
-      </c>
-      <c r="AP9">
-        <v>1.28</v>
-      </c>
-      <c r="AQ9">
-        <v>1.52</v>
-      </c>
-      <c r="AR9">
-        <v>1.92</v>
-      </c>
-      <c r="AS9">
-        <v>2.46</v>
-      </c>
-      <c r="AT9">
-        <v>3.34</v>
-      </c>
-      <c r="AU9">
-        <v>3.08</v>
-      </c>
-      <c r="AV9">
-        <v>2.24</v>
-      </c>
-      <c r="AW9">
-        <v>1.75</v>
-      </c>
-      <c r="AX9">
-        <v>1.43</v>
-      </c>
-      <c r="AY9">
-        <v>1.24</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>1.45</v>
-      </c>
-      <c r="BC9">
-        <v>3.25</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>188</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45756.5</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45756</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="F10" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>152</v>
+      </c>
+      <c r="L10">
+        <v>3.3</v>
+      </c>
+      <c r="M10">
+        <v>3.6</v>
+      </c>
+      <c r="N10">
+        <v>1.95</v>
+      </c>
+      <c r="O10">
+        <v>2.75</v>
+      </c>
+      <c r="P10">
+        <v>7.8</v>
+      </c>
+      <c r="Q10">
+        <v>1.57</v>
+      </c>
+      <c r="R10">
+        <v>1.44</v>
+      </c>
+      <c r="S10">
+        <v>2.62</v>
+      </c>
+      <c r="T10">
         <v>3</v>
       </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>3</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="s">
-        <v>170</v>
-      </c>
-      <c r="L10">
-        <v>1.4</v>
-      </c>
-      <c r="M10">
-        <v>4.6</v>
-      </c>
-      <c r="N10">
-        <v>6</v>
-      </c>
-      <c r="O10">
-        <v>1.3</v>
-      </c>
-      <c r="P10">
-        <v>15</v>
-      </c>
-      <c r="Q10">
-        <v>3.4</v>
-      </c>
-      <c r="R10">
-        <v>1.22</v>
-      </c>
-      <c r="S10">
-        <v>3.8</v>
-      </c>
-      <c r="T10">
-        <v>2.1</v>
-      </c>
       <c r="U10">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="V10">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="W10">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Z10">
-        <v>1.09</v>
+        <v>1.37</v>
       </c>
       <c r="AA10">
-        <v>6.25</v>
+        <v>2.66</v>
       </c>
       <c r="AB10">
-        <v>1.42</v>
+        <v>2.15</v>
       </c>
       <c r="AC10">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD10">
-        <v>2.15</v>
+        <v>4.15</v>
       </c>
       <c r="AE10">
-        <v>1.69</v>
+        <v>1.16</v>
       </c>
       <c r="AF10">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AG10">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AH10">
-        <v>3.55</v>
+        <v>8.5</v>
       </c>
       <c r="AI10">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="AK10" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL10">
-        <v>1.12</v>
-      </c>
-      <c r="AM10">
-        <v>1.19</v>
-      </c>
-      <c r="AN10">
-        <v>2.85</v>
-      </c>
-      <c r="AO10">
-        <v>7</v>
-      </c>
-      <c r="AP10">
-        <v>0</v>
-      </c>
-      <c r="AQ10">
-        <v>0</v>
-      </c>
-      <c r="AR10">
-        <v>0</v>
-      </c>
-      <c r="AS10">
-        <v>0</v>
-      </c>
-      <c r="AT10">
-        <v>0</v>
-      </c>
-      <c r="AU10">
-        <v>0</v>
-      </c>
-      <c r="AV10">
-        <v>0</v>
-      </c>
-      <c r="AW10">
-        <v>0</v>
-      </c>
-      <c r="AX10">
-        <v>0</v>
-      </c>
-      <c r="AY10">
-        <v>0</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>1.3</v>
-      </c>
-      <c r="BC10">
-        <v>3.4</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>189</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45756.5</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45756</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F11" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="s">
+        <v>152</v>
+      </c>
+      <c r="L11">
+        <v>1.29</v>
+      </c>
+      <c r="M11">
         <v>5</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>3</v>
-      </c>
-      <c r="K11" t="s">
-        <v>170</v>
-      </c>
-      <c r="L11">
-        <v>2.55</v>
-      </c>
-      <c r="M11">
-        <v>2.9</v>
-      </c>
       <c r="N11">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1.35</v>
       </c>
       <c r="P11">
-        <v>7.7</v>
+        <v>11.5</v>
       </c>
       <c r="Q11">
-        <v>2.11</v>
+        <v>3.6</v>
       </c>
       <c r="R11">
-        <v>1.49</v>
+        <v>1.2</v>
       </c>
       <c r="S11">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="U11">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="X11">
         <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>7.7</v>
+        <v>14</v>
       </c>
       <c r="Z11">
-        <v>1.39</v>
+        <v>1.13</v>
       </c>
       <c r="AA11">
-        <v>2.75</v>
+        <v>4.75</v>
       </c>
       <c r="AB11">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AC11">
-        <v>1.62</v>
+        <v>2.32</v>
       </c>
       <c r="AD11">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="AE11">
+        <v>1.53</v>
+      </c>
+      <c r="AF11">
+        <v>2</v>
+      </c>
+      <c r="AG11">
+        <v>1.73</v>
+      </c>
+      <c r="AH11">
+        <v>3.75</v>
+      </c>
+      <c r="AI11">
         <v>1.23</v>
       </c>
-      <c r="AF11">
-        <v>1.88</v>
-      </c>
-      <c r="AG11">
-        <v>1.83</v>
-      </c>
-      <c r="AH11">
-        <v>8.1</v>
-      </c>
-      <c r="AI11">
-        <v>1.02</v>
-      </c>
       <c r="AJ11" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="AK11" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL11">
-        <v>1.42</v>
-      </c>
-      <c r="AM11">
-        <v>1.33</v>
-      </c>
-      <c r="AN11">
-        <v>1.47</v>
-      </c>
-      <c r="AO11">
-        <v>13</v>
-      </c>
-      <c r="AP11">
-        <v>1.46</v>
-      </c>
-      <c r="AQ11">
-        <v>1.77</v>
-      </c>
-      <c r="AR11">
-        <v>2.23</v>
-      </c>
-      <c r="AS11">
-        <v>2.9</v>
-      </c>
-      <c r="AT11">
-        <v>3.9</v>
-      </c>
-      <c r="AU11">
-        <v>2.5</v>
-      </c>
-      <c r="AV11">
-        <v>1.92</v>
-      </c>
-      <c r="AW11">
-        <v>1.56</v>
-      </c>
-      <c r="AX11">
-        <v>1.34</v>
-      </c>
-      <c r="AY11">
-        <v>1.21</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>2</v>
-      </c>
-      <c r="BC11">
-        <v>2.11</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45756.54166666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45756</v>
       </c>
       <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="F12" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -2960,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L12">
         <v>1.25</v>
@@ -3035,502 +2387,340 @@
         <v>1.22</v>
       </c>
       <c r="AJ12" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="AK12" t="s">
-        <v>209</v>
-      </c>
-      <c r="AL12">
-        <v>1.07</v>
-      </c>
-      <c r="AM12">
-        <v>1.15</v>
-      </c>
-      <c r="AN12">
-        <v>3.2</v>
-      </c>
-      <c r="AO12">
-        <v>11</v>
-      </c>
-      <c r="AP12">
-        <v>1.11</v>
-      </c>
-      <c r="AQ12">
-        <v>1.22</v>
-      </c>
-      <c r="AR12">
-        <v>1.28</v>
-      </c>
-      <c r="AS12">
-        <v>1.62</v>
-      </c>
-      <c r="AT12">
-        <v>1.95</v>
-      </c>
-      <c r="AU12">
-        <v>5.5</v>
-      </c>
-      <c r="AV12">
-        <v>3.8</v>
-      </c>
-      <c r="AW12">
-        <v>2.97</v>
-      </c>
-      <c r="AX12">
-        <v>2.2</v>
-      </c>
-      <c r="AY12">
-        <v>1.75</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.22</v>
-      </c>
-      <c r="BC12">
-        <v>4.33</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>190</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45756.54166666666</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45756</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K13" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L13">
-        <v>1.29</v>
+        <v>2.75</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N13">
-        <v>7.8</v>
+        <v>2.35</v>
       </c>
       <c r="O13">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="P13">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="R13">
+        <v>1.44</v>
+      </c>
+      <c r="S13">
+        <v>2.62</v>
+      </c>
+      <c r="T13">
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <v>1.36</v>
+      </c>
+      <c r="V13">
+        <v>7.5</v>
+      </c>
+      <c r="W13">
+        <v>1.07</v>
+      </c>
+      <c r="X13">
+        <v>1.07</v>
+      </c>
+      <c r="Y13">
+        <v>8</v>
+      </c>
+      <c r="Z13">
+        <v>1.33</v>
+      </c>
+      <c r="AA13">
+        <v>2.83</v>
+      </c>
+      <c r="AB13">
+        <v>2.1</v>
+      </c>
+      <c r="AC13">
+        <v>1.61</v>
+      </c>
+      <c r="AD13">
+        <v>3.7</v>
+      </c>
+      <c r="AE13">
         <v>1.2</v>
       </c>
-      <c r="S13">
-        <v>3.8</v>
-      </c>
-      <c r="T13">
-        <v>2.3</v>
-      </c>
-      <c r="U13">
-        <v>1.6</v>
-      </c>
-      <c r="V13">
-        <v>4.4</v>
-      </c>
-      <c r="W13">
-        <v>1.15</v>
-      </c>
-      <c r="X13">
-        <v>1.03</v>
-      </c>
-      <c r="Y13">
-        <v>14</v>
-      </c>
-      <c r="Z13">
-        <v>1.13</v>
-      </c>
-      <c r="AA13">
-        <v>4.75</v>
-      </c>
-      <c r="AB13">
-        <v>1.55</v>
-      </c>
-      <c r="AC13">
-        <v>2.32</v>
-      </c>
-      <c r="AD13">
-        <v>2.5</v>
-      </c>
-      <c r="AE13">
-        <v>1.53</v>
-      </c>
       <c r="AF13">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG13">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AH13">
-        <v>3.75</v>
+        <v>8.5</v>
       </c>
       <c r="AI13">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="AJ13" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="AK13" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL13">
-        <v>1.15</v>
-      </c>
-      <c r="AM13">
-        <v>1.19</v>
-      </c>
-      <c r="AN13">
-        <v>3.4</v>
-      </c>
-      <c r="AO13">
-        <v>8</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.35</v>
-      </c>
-      <c r="BC13">
-        <v>3.6</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>191</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45756.54166666666</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45756</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I14">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L14">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="M14">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N14">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="O14">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="P14">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="R14">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S14">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="T14">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="V14">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>1.06</v>
       </c>
       <c r="X14">
+        <v>1.03</v>
+      </c>
+      <c r="Y14">
+        <v>7.7</v>
+      </c>
+      <c r="Z14">
+        <v>1.39</v>
+      </c>
+      <c r="AA14">
+        <v>2.75</v>
+      </c>
+      <c r="AB14">
+        <v>2.2</v>
+      </c>
+      <c r="AC14">
+        <v>1.62</v>
+      </c>
+      <c r="AD14">
+        <v>3.95</v>
+      </c>
+      <c r="AE14">
+        <v>1.23</v>
+      </c>
+      <c r="AF14">
+        <v>1.88</v>
+      </c>
+      <c r="AG14">
+        <v>1.83</v>
+      </c>
+      <c r="AH14">
+        <v>8.1</v>
+      </c>
+      <c r="AI14">
         <v>1.02</v>
       </c>
-      <c r="Y14">
-        <v>8.5</v>
-      </c>
-      <c r="Z14">
-        <v>1.36</v>
-      </c>
-      <c r="AA14">
-        <v>2.81</v>
-      </c>
-      <c r="AB14">
-        <v>2.1</v>
-      </c>
-      <c r="AC14">
-        <v>1.65</v>
-      </c>
-      <c r="AD14">
-        <v>3.85</v>
-      </c>
-      <c r="AE14">
-        <v>1.22</v>
-      </c>
-      <c r="AF14">
-        <v>1.85</v>
-      </c>
-      <c r="AG14">
-        <v>1.85</v>
-      </c>
-      <c r="AH14">
-        <v>7.7</v>
-      </c>
-      <c r="AI14">
-        <v>1.06</v>
-      </c>
       <c r="AJ14" t="s">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="AK14" t="s">
-        <v>210</v>
-      </c>
-      <c r="AL14">
-        <v>1.32</v>
-      </c>
-      <c r="AM14">
-        <v>1.28</v>
-      </c>
-      <c r="AN14">
-        <v>1.65</v>
-      </c>
-      <c r="AO14">
-        <v>8</v>
-      </c>
-      <c r="AP14">
-        <v>1.4</v>
-      </c>
-      <c r="AQ14">
-        <v>1.8</v>
-      </c>
-      <c r="AR14">
-        <v>2.3</v>
-      </c>
-      <c r="AS14">
-        <v>3.08</v>
-      </c>
-      <c r="AT14">
-        <v>3.8</v>
-      </c>
-      <c r="AU14">
-        <v>2.56</v>
-      </c>
-      <c r="AV14">
-        <v>1.89</v>
-      </c>
-      <c r="AW14">
-        <v>1.52</v>
-      </c>
-      <c r="AX14">
-        <v>1.35</v>
-      </c>
-      <c r="AY14">
-        <v>1.14</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.67</v>
-      </c>
-      <c r="BC14">
-        <v>2.5</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>192</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45756.54166666666</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45756</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
         <v>1</v>
       </c>
-      <c r="H15">
-        <v>2</v>
-      </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L15">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="M15">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N15">
-        <v>2.35</v>
+        <v>3.05</v>
       </c>
       <c r="O15">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="P15">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q15">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S15">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T15">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
+        <v>1.3</v>
+      </c>
+      <c r="V15">
+        <v>8.75</v>
+      </c>
+      <c r="W15">
+        <v>1.06</v>
+      </c>
+      <c r="X15">
+        <v>1.02</v>
+      </c>
+      <c r="Y15">
+        <v>8.5</v>
+      </c>
+      <c r="Z15">
         <v>1.36</v>
       </c>
-      <c r="V15">
-        <v>7.5</v>
-      </c>
-      <c r="W15">
-        <v>1.07</v>
-      </c>
-      <c r="X15">
-        <v>1.07</v>
-      </c>
-      <c r="Y15">
-        <v>8</v>
-      </c>
-      <c r="Z15">
-        <v>1.33</v>
-      </c>
       <c r="AA15">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AB15">
         <v>2.1</v>
       </c>
       <c r="AC15">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AD15">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AE15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
         <v>1.85</v>
@@ -3539,263 +2729,155 @@
         <v>1.85</v>
       </c>
       <c r="AH15">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="AI15">
         <v>1.06</v>
       </c>
       <c r="AJ15" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="AK15" t="s">
-        <v>211</v>
-      </c>
-      <c r="AL15">
-        <v>1.5</v>
-      </c>
-      <c r="AM15">
-        <v>1.3</v>
-      </c>
-      <c r="AN15">
-        <v>1.44</v>
-      </c>
-      <c r="AO15">
-        <v>14</v>
-      </c>
-      <c r="AP15">
-        <v>0</v>
-      </c>
-      <c r="AQ15">
-        <v>0</v>
-      </c>
-      <c r="AR15">
-        <v>0</v>
-      </c>
-      <c r="AS15">
-        <v>0</v>
-      </c>
-      <c r="AT15">
-        <v>0</v>
-      </c>
-      <c r="AU15">
-        <v>0</v>
-      </c>
-      <c r="AV15">
-        <v>0</v>
-      </c>
-      <c r="AW15">
-        <v>0</v>
-      </c>
-      <c r="AX15">
-        <v>0</v>
-      </c>
-      <c r="AY15">
-        <v>0</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>2.25</v>
-      </c>
-      <c r="BC15">
-        <v>1.8</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>193</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45756.54166666666</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45756</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L16">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="M16">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N16">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O16">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P16">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Q16">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="R16">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S16">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T16">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="U16">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Z16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AA16">
-        <v>4.17</v>
+        <v>4.2</v>
       </c>
       <c r="AB16">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AC16">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD16">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AE16">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF16">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AH16">
-        <v>4.99</v>
+        <v>4.6</v>
       </c>
       <c r="AI16">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AJ16" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="AK16" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL16">
-        <v>1.3</v>
-      </c>
-      <c r="AM16">
-        <v>1.25</v>
-      </c>
-      <c r="AN16">
-        <v>1.75</v>
-      </c>
-      <c r="AO16">
-        <v>10</v>
-      </c>
-      <c r="AP16">
-        <v>1.19</v>
-      </c>
-      <c r="AQ16">
-        <v>1.38</v>
-      </c>
-      <c r="AR16">
-        <v>1.69</v>
-      </c>
-      <c r="AS16">
-        <v>2.12</v>
-      </c>
-      <c r="AT16">
-        <v>2.81</v>
-      </c>
-      <c r="AU16">
-        <v>3.8</v>
-      </c>
-      <c r="AV16">
-        <v>2.62</v>
-      </c>
-      <c r="AW16">
-        <v>2</v>
-      </c>
-      <c r="AX16">
-        <v>1.58</v>
-      </c>
-      <c r="AY16">
-        <v>1.33</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.75</v>
-      </c>
-      <c r="BC16">
-        <v>2.35</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>194</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45756.58333333334</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45756</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3810,7 +2892,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L17">
         <v>1.75</v>
@@ -3885,87 +2967,33 @@
         <v>1.15</v>
       </c>
       <c r="AJ17" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AK17" t="s">
-        <v>196</v>
-      </c>
-      <c r="AL17">
-        <v>1.2</v>
-      </c>
-      <c r="AM17">
-        <v>1.22</v>
-      </c>
-      <c r="AN17">
-        <v>1.9</v>
-      </c>
-      <c r="AO17">
-        <v>-1</v>
-      </c>
-      <c r="AP17">
-        <v>1.22</v>
-      </c>
-      <c r="AQ17">
-        <v>1.3</v>
-      </c>
-      <c r="AR17">
-        <v>1.54</v>
-      </c>
-      <c r="AS17">
-        <v>1.92</v>
-      </c>
-      <c r="AT17">
-        <v>2.46</v>
-      </c>
-      <c r="AU17">
-        <v>3.8</v>
-      </c>
-      <c r="AV17">
-        <v>2.97</v>
-      </c>
-      <c r="AW17">
-        <v>2.19</v>
-      </c>
-      <c r="AX17">
-        <v>1.75</v>
-      </c>
-      <c r="AY17">
-        <v>1.43</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.67</v>
-      </c>
-      <c r="BC17">
-        <v>2.5</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>178</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45756.58333333334</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45756</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
         <v>90</v>
       </c>
-      <c r="E18" t="s">
-        <v>108</v>
-      </c>
       <c r="F18" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -3974,851 +3002,581 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L18">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="M18">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N18">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="P18">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="R18">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S18">
+        <v>3</v>
+      </c>
+      <c r="T18">
+        <v>2.45</v>
+      </c>
+      <c r="U18">
+        <v>1.48</v>
+      </c>
+      <c r="V18">
+        <v>6</v>
+      </c>
+      <c r="W18">
+        <v>1.06</v>
+      </c>
+      <c r="X18">
+        <v>1.04</v>
+      </c>
+      <c r="Y18">
+        <v>9</v>
+      </c>
+      <c r="Z18">
+        <v>1.22</v>
+      </c>
+      <c r="AA18">
+        <v>4.17</v>
+      </c>
+      <c r="AB18">
+        <v>1.73</v>
+      </c>
+      <c r="AC18">
+        <v>2</v>
+      </c>
+      <c r="AD18">
         <v>2.75</v>
       </c>
-      <c r="T18">
-        <v>3</v>
-      </c>
-      <c r="U18">
-        <v>1.36</v>
-      </c>
-      <c r="V18">
-        <v>8</v>
-      </c>
-      <c r="W18">
-        <v>1.08</v>
-      </c>
-      <c r="X18">
-        <v>1.06</v>
-      </c>
-      <c r="Y18">
-        <v>8.5</v>
-      </c>
-      <c r="Z18">
-        <v>1.33</v>
-      </c>
-      <c r="AA18">
-        <v>3.25</v>
-      </c>
-      <c r="AB18">
-        <v>1.98</v>
-      </c>
-      <c r="AC18">
-        <v>1.77</v>
-      </c>
-      <c r="AD18">
-        <v>3.45</v>
-      </c>
       <c r="AE18">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AF18">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AH18">
-        <v>7</v>
+        <v>4.99</v>
       </c>
       <c r="AI18">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AJ18" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="AK18" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL18">
-        <v>1.42</v>
-      </c>
-      <c r="AM18">
-        <v>1.32</v>
-      </c>
-      <c r="AN18">
-        <v>1.5</v>
-      </c>
-      <c r="AO18">
-        <v>11</v>
-      </c>
-      <c r="AP18">
-        <v>1.21</v>
-      </c>
-      <c r="AQ18">
-        <v>1.38</v>
-      </c>
-      <c r="AR18">
-        <v>1.63</v>
-      </c>
-      <c r="AS18">
-        <v>1.96</v>
-      </c>
-      <c r="AT18">
-        <v>2.43</v>
-      </c>
-      <c r="AU18">
-        <v>3.9</v>
-      </c>
-      <c r="AV18">
-        <v>2.8</v>
-      </c>
-      <c r="AW18">
-        <v>2.15</v>
-      </c>
-      <c r="AX18">
-        <v>1.74</v>
-      </c>
-      <c r="AY18">
-        <v>1.48</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>1.8</v>
-      </c>
-      <c r="BC18">
-        <v>2.2</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45756.58333333334</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45756</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
         <v>91</v>
       </c>
-      <c r="E19" t="s">
-        <v>109</v>
-      </c>
       <c r="F19" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L19">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="M19">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="N19">
-        <v>4.38</v>
+        <v>2.9</v>
       </c>
       <c r="O19">
-        <v>1.57</v>
+        <v>1.93</v>
       </c>
       <c r="P19">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="R19">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S19">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="T19">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="V19">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Z19">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AA19">
-        <v>4.27</v>
+        <v>3.4</v>
       </c>
       <c r="AB19">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC19">
-        <v>2.19</v>
+        <v>1.97</v>
       </c>
       <c r="AD19">
-        <v>2.61</v>
+        <v>3.1</v>
       </c>
       <c r="AE19">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AF19">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH19">
-        <v>4.66</v>
+        <v>5.7</v>
       </c>
       <c r="AI19">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AJ19" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="AK19" t="s">
-        <v>212</v>
-      </c>
-      <c r="AL19">
-        <v>1.17</v>
-      </c>
-      <c r="AM19">
-        <v>1.2</v>
-      </c>
-      <c r="AN19">
-        <v>2.05</v>
-      </c>
-      <c r="AO19">
-        <v>11</v>
-      </c>
-      <c r="AP19">
-        <v>1.2</v>
-      </c>
-      <c r="AQ19">
-        <v>1.28</v>
-      </c>
-      <c r="AR19">
-        <v>1.51</v>
-      </c>
-      <c r="AS19">
-        <v>1.88</v>
-      </c>
-      <c r="AT19">
-        <v>2.38</v>
-      </c>
-      <c r="AU19">
-        <v>4</v>
-      </c>
-      <c r="AV19">
-        <v>3.08</v>
-      </c>
-      <c r="AW19">
-        <v>2.26</v>
-      </c>
-      <c r="AX19">
-        <v>1.78</v>
-      </c>
-      <c r="AY19">
-        <v>1.46</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1.57</v>
-      </c>
-      <c r="BC19">
-        <v>2.62</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>195</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45756.58333333334</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45756</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="F20" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>1</v>
       </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
       <c r="J20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L20">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="M20">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="N20">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="O20">
         <v>1.8</v>
       </c>
       <c r="P20">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="Q20">
         <v>2.2</v>
       </c>
       <c r="R20">
+        <v>1.4</v>
+      </c>
+      <c r="S20">
+        <v>2.75</v>
+      </c>
+      <c r="T20">
+        <v>3</v>
+      </c>
+      <c r="U20">
+        <v>1.36</v>
+      </c>
+      <c r="V20">
+        <v>8</v>
+      </c>
+      <c r="W20">
+        <v>1.08</v>
+      </c>
+      <c r="X20">
+        <v>1.06</v>
+      </c>
+      <c r="Y20">
+        <v>8.5</v>
+      </c>
+      <c r="Z20">
+        <v>1.33</v>
+      </c>
+      <c r="AA20">
+        <v>3.25</v>
+      </c>
+      <c r="AB20">
+        <v>1.98</v>
+      </c>
+      <c r="AC20">
+        <v>1.77</v>
+      </c>
+      <c r="AD20">
+        <v>3.45</v>
+      </c>
+      <c r="AE20">
         <v>1.3</v>
       </c>
-      <c r="S20">
-        <v>3.2</v>
-      </c>
-      <c r="T20">
-        <v>2.3</v>
-      </c>
-      <c r="U20">
-        <v>1.55</v>
-      </c>
-      <c r="V20">
-        <v>5.8</v>
-      </c>
-      <c r="W20">
-        <v>1.07</v>
-      </c>
-      <c r="X20">
-        <v>1.04</v>
-      </c>
-      <c r="Y20">
-        <v>9.5</v>
-      </c>
-      <c r="Z20">
-        <v>1.2</v>
-      </c>
-      <c r="AA20">
-        <v>4.2</v>
-      </c>
-      <c r="AB20">
-        <v>1.58</v>
-      </c>
-      <c r="AC20">
-        <v>2.2</v>
-      </c>
-      <c r="AD20">
-        <v>2.5</v>
-      </c>
-      <c r="AE20">
-        <v>1.5</v>
-      </c>
       <c r="AF20">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AG20">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AH20">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AI20">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AJ20" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="AK20" t="s">
-        <v>213</v>
-      </c>
-      <c r="AL20">
-        <v>1.33</v>
-      </c>
-      <c r="AM20">
-        <v>1.22</v>
-      </c>
-      <c r="AN20">
-        <v>1.67</v>
-      </c>
-      <c r="AO20">
-        <v>11</v>
-      </c>
-      <c r="AP20">
-        <v>1.19</v>
-      </c>
-      <c r="AQ20">
-        <v>1.38</v>
-      </c>
-      <c r="AR20">
-        <v>1.69</v>
-      </c>
-      <c r="AS20">
-        <v>2.1</v>
-      </c>
-      <c r="AT20">
-        <v>2.78</v>
-      </c>
-      <c r="AU20">
-        <v>3.82</v>
-      </c>
-      <c r="AV20">
-        <v>2.62</v>
-      </c>
-      <c r="AW20">
-        <v>2</v>
-      </c>
-      <c r="AX20">
-        <v>1.59</v>
-      </c>
-      <c r="AY20">
-        <v>1.34</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>1.8</v>
-      </c>
-      <c r="BC20">
-        <v>2.2</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45756.58333333334</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45756</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>83</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="F21" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L21">
-        <v>2.39</v>
+        <v>2.13</v>
       </c>
       <c r="M21">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="N21">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O21">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="P21">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q21">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="R21">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S21">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="T21">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="U21">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V21">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="W21">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X21">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="Z21">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AA21">
-        <v>3.4</v>
+        <v>2.92</v>
       </c>
       <c r="AB21">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="AC21">
-        <v>1.97</v>
+        <v>1.68</v>
       </c>
       <c r="AD21">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="AE21">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AF21">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AG21">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AH21">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AI21">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AJ21" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="AK21" t="s">
-        <v>214</v>
-      </c>
-      <c r="AL21">
-        <v>1.4</v>
-      </c>
-      <c r="AM21">
-        <v>1.25</v>
-      </c>
-      <c r="AN21">
-        <v>1.55</v>
-      </c>
-      <c r="AO21">
-        <v>7</v>
-      </c>
-      <c r="AP21">
-        <v>1.25</v>
-      </c>
-      <c r="AQ21">
-        <v>1.35</v>
-      </c>
-      <c r="AR21">
-        <v>1.62</v>
-      </c>
-      <c r="AS21">
-        <v>2.05</v>
-      </c>
-      <c r="AT21">
-        <v>2.66</v>
-      </c>
-      <c r="AU21">
-        <v>3.6</v>
-      </c>
-      <c r="AV21">
-        <v>2.74</v>
-      </c>
-      <c r="AW21">
-        <v>2.06</v>
-      </c>
-      <c r="AX21">
-        <v>1.65</v>
-      </c>
-      <c r="AY21">
-        <v>1.37</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1.93</v>
-      </c>
-      <c r="BC21">
-        <v>2.1</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>196</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45756.58333333334</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45756</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22">
+        <v>2</v>
+      </c>
+      <c r="I22">
         <v>1</v>
-      </c>
-      <c r="I22">
-        <v>2</v>
       </c>
       <c r="J22">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L22">
-        <v>2.27</v>
+        <v>1.72</v>
       </c>
       <c r="M22">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="N22">
-        <v>3.08</v>
+        <v>4.38</v>
       </c>
       <c r="O22">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="P22">
-        <v>11.25</v>
+        <v>10</v>
       </c>
       <c r="Q22">
+        <v>2.62</v>
+      </c>
+      <c r="R22">
+        <v>1.3</v>
+      </c>
+      <c r="S22">
+        <v>3.2</v>
+      </c>
+      <c r="T22">
+        <v>2.38</v>
+      </c>
+      <c r="U22">
+        <v>1.53</v>
+      </c>
+      <c r="V22">
+        <v>5.75</v>
+      </c>
+      <c r="W22">
+        <v>1.07</v>
+      </c>
+      <c r="X22">
+        <v>1.03</v>
+      </c>
+      <c r="Y22">
+        <v>10</v>
+      </c>
+      <c r="Z22">
+        <v>1.2</v>
+      </c>
+      <c r="AA22">
+        <v>4.27</v>
+      </c>
+      <c r="AB22">
+        <v>1.66</v>
+      </c>
+      <c r="AC22">
+        <v>2.19</v>
+      </c>
+      <c r="AD22">
+        <v>2.61</v>
+      </c>
+      <c r="AE22">
+        <v>1.46</v>
+      </c>
+      <c r="AF22">
+        <v>1.57</v>
+      </c>
+      <c r="AG22">
         <v>2.15</v>
       </c>
-      <c r="R22">
-        <v>1.37</v>
-      </c>
-      <c r="S22">
-        <v>2.84</v>
-      </c>
-      <c r="T22">
-        <v>2.84</v>
-      </c>
-      <c r="U22">
-        <v>1.37</v>
-      </c>
-      <c r="V22">
-        <v>7.3</v>
-      </c>
-      <c r="W22">
-        <v>1.03</v>
-      </c>
-      <c r="X22">
-        <v>1.06</v>
-      </c>
-      <c r="Y22">
-        <v>7.2</v>
-      </c>
-      <c r="Z22">
-        <v>1.25</v>
-      </c>
-      <c r="AA22">
-        <v>3.28</v>
-      </c>
-      <c r="AB22">
-        <v>1.95</v>
-      </c>
-      <c r="AC22">
-        <v>1.84</v>
-      </c>
-      <c r="AD22">
-        <v>3.28</v>
-      </c>
-      <c r="AE22">
-        <v>1.25</v>
-      </c>
-      <c r="AF22">
-        <v>1.71</v>
-      </c>
-      <c r="AG22">
-        <v>1.97</v>
-      </c>
       <c r="AH22">
-        <v>6.55</v>
+        <v>4.66</v>
       </c>
       <c r="AI22">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AJ22" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="AK22" t="s">
-        <v>215</v>
-      </c>
-      <c r="AL22">
-        <v>1.33</v>
-      </c>
-      <c r="AM22">
-        <v>1.27</v>
-      </c>
-      <c r="AN22">
-        <v>1.59</v>
-      </c>
-      <c r="AO22">
-        <v>11</v>
-      </c>
-      <c r="AP22">
-        <v>1.4</v>
-      </c>
-      <c r="AQ22">
-        <v>1.75</v>
-      </c>
-      <c r="AR22">
-        <v>2.24</v>
-      </c>
-      <c r="AS22">
-        <v>3.05</v>
-      </c>
-      <c r="AT22">
-        <v>3.8</v>
-      </c>
-      <c r="AU22">
-        <v>2.56</v>
-      </c>
-      <c r="AV22">
-        <v>1.92</v>
-      </c>
-      <c r="AW22">
-        <v>1.52</v>
-      </c>
-      <c r="AX22">
-        <v>1.28</v>
-      </c>
-      <c r="AY22">
-        <v>1.22</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>1.78</v>
-      </c>
-      <c r="BC22">
-        <v>2.15</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>197</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45756.58333333334</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45756</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="D23" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F23" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -4827,165 +3585,111 @@
         <v>2</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L23">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="M23">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="N23">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="O23">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="P23">
-        <v>8.1</v>
+        <v>11.25</v>
       </c>
       <c r="Q23">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="S23">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="T23">
-        <v>3.04</v>
+        <v>2.84</v>
       </c>
       <c r="U23">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="V23">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="W23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y23">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="Z23">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AA23">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="AB23">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AD23">
-        <v>3.58</v>
+        <v>3.28</v>
       </c>
       <c r="AE23">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF23">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AG23">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AH23">
-        <v>7.2</v>
+        <v>6.55</v>
       </c>
       <c r="AI23">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ23" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="AK23" t="s">
-        <v>216</v>
-      </c>
-      <c r="AL23">
-        <v>1.27</v>
-      </c>
-      <c r="AM23">
-        <v>1.28</v>
-      </c>
-      <c r="AN23">
-        <v>1.65</v>
-      </c>
-      <c r="AO23">
-        <v>5</v>
-      </c>
-      <c r="AP23">
-        <v>1.44</v>
-      </c>
-      <c r="AQ23">
-        <v>1.83</v>
-      </c>
-      <c r="AR23">
-        <v>2.35</v>
-      </c>
-      <c r="AS23">
-        <v>3.28</v>
-      </c>
-      <c r="AT23">
-        <v>4</v>
-      </c>
-      <c r="AU23">
-        <v>2.42</v>
-      </c>
-      <c r="AV23">
-        <v>1.83</v>
-      </c>
-      <c r="AW23">
-        <v>1.47</v>
-      </c>
-      <c r="AX23">
-        <v>1.25</v>
-      </c>
-      <c r="AY23">
-        <v>1.2</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>1.76</v>
-      </c>
-      <c r="BC23">
-        <v>2.35</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>198</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45756.58333333334</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45756</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="F24" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="G24">
         <v>2</v>
@@ -5000,7 +3704,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L24">
         <v>1.78</v>
@@ -5075,87 +3779,33 @@
         <v>1.12</v>
       </c>
       <c r="AJ24" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="AK24" t="s">
-        <v>217</v>
-      </c>
-      <c r="AL24">
-        <v>1.29</v>
-      </c>
-      <c r="AM24">
-        <v>1.22</v>
-      </c>
-      <c r="AN24">
-        <v>1.95</v>
-      </c>
-      <c r="AO24">
-        <v>11</v>
-      </c>
-      <c r="AP24">
-        <v>1.15</v>
-      </c>
-      <c r="AQ24">
-        <v>1.26</v>
-      </c>
-      <c r="AR24">
-        <v>1.64</v>
-      </c>
-      <c r="AS24">
-        <v>1.83</v>
-      </c>
-      <c r="AT24">
-        <v>2.3</v>
-      </c>
-      <c r="AU24">
-        <v>4.5</v>
-      </c>
-      <c r="AV24">
-        <v>3.22</v>
-      </c>
-      <c r="AW24">
-        <v>2.37</v>
-      </c>
-      <c r="AX24">
-        <v>1.83</v>
-      </c>
-      <c r="AY24">
-        <v>1.49</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>1.7</v>
-      </c>
-      <c r="BC24">
-        <v>2.4</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>199</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45756.64583333334</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45756</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="D25" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5170,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L25">
         <v>3.17</v>
@@ -5245,87 +3895,33 @@
         <v>1.08</v>
       </c>
       <c r="AJ25" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AK25" t="s">
-        <v>218</v>
-      </c>
-      <c r="AL25">
-        <v>1.7</v>
-      </c>
-      <c r="AM25">
-        <v>1.28</v>
-      </c>
-      <c r="AN25">
-        <v>1.3</v>
-      </c>
-      <c r="AO25">
-        <v>14</v>
-      </c>
-      <c r="AP25">
-        <v>1.26</v>
-      </c>
-      <c r="AQ25">
-        <v>1.46</v>
-      </c>
-      <c r="AR25">
-        <v>1.81</v>
-      </c>
-      <c r="AS25">
-        <v>2.33</v>
-      </c>
-      <c r="AT25">
-        <v>2.51</v>
-      </c>
-      <c r="AU25">
-        <v>3.42</v>
-      </c>
-      <c r="AV25">
-        <v>2.55</v>
-      </c>
-      <c r="AW25">
-        <v>1.9</v>
-      </c>
-      <c r="AX25">
-        <v>1.56</v>
-      </c>
-      <c r="AY25">
-        <v>1.28</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>2.2</v>
-      </c>
-      <c r="BC25">
-        <v>1.9</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>200</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45756.64583333334</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45756</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -5340,7 +3936,7 @@
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L26">
         <v>2.61</v>
@@ -5415,87 +4011,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ26" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK26" t="s">
-        <v>219</v>
-      </c>
-      <c r="AL26">
-        <v>1.45</v>
-      </c>
-      <c r="AM26">
-        <v>1.3</v>
-      </c>
-      <c r="AN26">
-        <v>1.45</v>
-      </c>
-      <c r="AO26">
-        <v>14</v>
-      </c>
-      <c r="AP26">
-        <v>1.25</v>
-      </c>
-      <c r="AQ26">
-        <v>1.44</v>
-      </c>
-      <c r="AR26">
-        <v>1.72</v>
-      </c>
-      <c r="AS26">
-        <v>2.1</v>
-      </c>
-      <c r="AT26">
-        <v>2.7</v>
-      </c>
-      <c r="AU26">
-        <v>3.45</v>
-      </c>
-      <c r="AV26">
-        <v>2.55</v>
-      </c>
-      <c r="AW26">
-        <v>1.98</v>
-      </c>
-      <c r="AX26">
-        <v>1.64</v>
-      </c>
-      <c r="AY26">
-        <v>1.4</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>2</v>
-      </c>
-      <c r="BC26">
-        <v>2</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>201</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45756.65625</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45756</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F27" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G27">
         <v>3</v>
@@ -5510,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L27">
         <v>1.72</v>
@@ -5585,257 +4127,149 @@
         <v>1.09</v>
       </c>
       <c r="AJ27" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="AK27" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL27">
-        <v>1.17</v>
-      </c>
-      <c r="AM27">
-        <v>1.2</v>
-      </c>
-      <c r="AN27">
-        <v>2.2</v>
-      </c>
-      <c r="AO27">
-        <v>4</v>
-      </c>
-      <c r="AP27">
-        <v>1.23</v>
-      </c>
-      <c r="AQ27">
-        <v>1.41</v>
-      </c>
-      <c r="AR27">
-        <v>1.66</v>
-      </c>
-      <c r="AS27">
-        <v>2</v>
-      </c>
-      <c r="AT27">
-        <v>2.55</v>
-      </c>
-      <c r="AU27">
-        <v>3.65</v>
-      </c>
-      <c r="AV27">
-        <v>2.65</v>
-      </c>
-      <c r="AW27">
-        <v>2.07</v>
-      </c>
-      <c r="AX27">
-        <v>1.71</v>
-      </c>
-      <c r="AY27">
-        <v>1.44</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>1.44</v>
-      </c>
-      <c r="BC27">
-        <v>3.2</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45756.65625</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45756</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="F28" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G28">
+        <v>4</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>1</v>
       </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L28">
-        <v>1.66</v>
+        <v>1.39</v>
       </c>
       <c r="M28">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="N28">
-        <v>4.7</v>
+        <v>7.5</v>
       </c>
       <c r="O28">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="P28">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="Q28">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R28">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="S28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T28">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="U28">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="V28">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="W28">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>10</v>
+        <v>19.5</v>
       </c>
       <c r="Z28">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AA28">
-        <v>3.8</v>
+        <v>5.95</v>
       </c>
       <c r="AB28">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AC28">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD28">
-        <v>3.1</v>
+        <v>2.01</v>
       </c>
       <c r="AE28">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="AF28">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH28">
-        <v>5.75</v>
+        <v>3.34</v>
       </c>
       <c r="AI28">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AJ28" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="AK28" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL28">
-        <v>1.17</v>
-      </c>
-      <c r="AM28">
-        <v>1.2</v>
-      </c>
-      <c r="AN28">
-        <v>2.2</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>1.14</v>
-      </c>
-      <c r="AQ28">
-        <v>1.25</v>
-      </c>
-      <c r="AR28">
-        <v>1.41</v>
-      </c>
-      <c r="AS28">
-        <v>1.67</v>
-      </c>
-      <c r="AT28">
-        <v>2</v>
-      </c>
-      <c r="AU28">
-        <v>4.8</v>
-      </c>
-      <c r="AV28">
-        <v>3.45</v>
-      </c>
-      <c r="AW28">
-        <v>2.63</v>
-      </c>
-      <c r="AX28">
-        <v>2.05</v>
-      </c>
-      <c r="AY28">
-        <v>1.7</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>1.44</v>
-      </c>
-      <c r="BC28">
-        <v>3</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45756.66666666666</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45756</v>
       </c>
       <c r="B29" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E29" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="F29" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="G29">
         <v>3</v>
@@ -5850,7 +4284,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L29">
         <v>1.42</v>
@@ -5925,257 +4359,149 @@
         <v>1.23</v>
       </c>
       <c r="AJ29" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="AK29" t="s">
-        <v>220</v>
-      </c>
-      <c r="AL29">
-        <v>1.1</v>
-      </c>
-      <c r="AM29">
-        <v>1.17</v>
-      </c>
-      <c r="AN29">
-        <v>2.8</v>
-      </c>
-      <c r="AO29">
-        <v>10</v>
-      </c>
-      <c r="AP29">
-        <v>1.2</v>
-      </c>
-      <c r="AQ29">
-        <v>1.36</v>
-      </c>
-      <c r="AR29">
-        <v>1.58</v>
-      </c>
-      <c r="AS29">
-        <v>1.92</v>
-      </c>
-      <c r="AT29">
-        <v>2.4</v>
-      </c>
-      <c r="AU29">
-        <v>3.9</v>
-      </c>
-      <c r="AV29">
-        <v>2.8</v>
-      </c>
-      <c r="AW29">
-        <v>2.18</v>
-      </c>
-      <c r="AX29">
-        <v>1.77</v>
-      </c>
-      <c r="AY29">
-        <v>1.5</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.29</v>
-      </c>
-      <c r="BC29">
-        <v>3.75</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>202</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45756.66666666666</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45756</v>
       </c>
       <c r="B30" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C30" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L30">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="M30">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="N30">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="O30">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="P30">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="R30">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="S30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="U30">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="V30">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y30">
-        <v>19.5</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="AA30">
-        <v>5.95</v>
+        <v>3.8</v>
       </c>
       <c r="AB30">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AC30">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD30">
-        <v>2.01</v>
+        <v>3.1</v>
       </c>
       <c r="AE30">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="AF30">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG30">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AH30">
-        <v>3.34</v>
+        <v>5.75</v>
       </c>
       <c r="AI30">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AJ30" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="AK30" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL30">
-        <v>1.1</v>
-      </c>
-      <c r="AM30">
-        <v>1.16</v>
-      </c>
-      <c r="AN30">
-        <v>2.95</v>
-      </c>
-      <c r="AO30">
-        <v>10</v>
-      </c>
-      <c r="AP30">
-        <v>1.2</v>
-      </c>
-      <c r="AQ30">
-        <v>1.35</v>
-      </c>
-      <c r="AR30">
-        <v>1.58</v>
-      </c>
-      <c r="AS30">
-        <v>1.91</v>
-      </c>
-      <c r="AT30">
-        <v>2.4</v>
-      </c>
-      <c r="AU30">
-        <v>3.95</v>
-      </c>
-      <c r="AV30">
-        <v>2.9</v>
-      </c>
-      <c r="AW30">
-        <v>2.2</v>
-      </c>
-      <c r="AX30">
-        <v>1.77</v>
-      </c>
-      <c r="AY30">
-        <v>1.5</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>1.29</v>
-      </c>
-      <c r="BC30">
-        <v>3.5</v>
-      </c>
-      <c r="BD30" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL30" s="3">
         <v>45756.66666666666</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45756</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="F31" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="G31">
         <v>1</v>
@@ -6190,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L31">
         <v>2.4</v>
@@ -6265,87 +4591,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ31" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="AK31" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL31">
-        <v>1.4</v>
-      </c>
-      <c r="AM31">
-        <v>1.36</v>
-      </c>
-      <c r="AN31">
-        <v>1.35</v>
-      </c>
-      <c r="AO31">
-        <v>7</v>
-      </c>
-      <c r="AP31">
-        <v>1.67</v>
-      </c>
-      <c r="AQ31">
-        <v>2</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31">
-        <v>2.1</v>
-      </c>
-      <c r="AV31">
-        <v>1.8</v>
-      </c>
-      <c r="AW31">
-        <v>0</v>
-      </c>
-      <c r="AX31">
-        <v>0</v>
-      </c>
-      <c r="AY31">
-        <v>0</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>1.73</v>
-      </c>
-      <c r="BC31">
-        <v>2.5</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45756.75</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45756</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E32" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="F32" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -6360,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L32">
         <v>2.4</v>
@@ -6435,87 +4707,33 @@
         <v>1.07</v>
       </c>
       <c r="AJ32" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AK32" t="s">
-        <v>221</v>
-      </c>
-      <c r="AL32">
-        <v>1.47</v>
-      </c>
-      <c r="AM32">
-        <v>1.33</v>
-      </c>
-      <c r="AN32">
-        <v>1.44</v>
-      </c>
-      <c r="AO32">
-        <v>9</v>
-      </c>
-      <c r="AP32">
-        <v>1.33</v>
-      </c>
-      <c r="AQ32">
-        <v>1.62</v>
-      </c>
-      <c r="AR32">
-        <v>2.05</v>
-      </c>
-      <c r="AS32">
-        <v>2.85</v>
-      </c>
-      <c r="AT32">
-        <v>4.1</v>
-      </c>
-      <c r="AU32">
-        <v>2.9</v>
-      </c>
-      <c r="AV32">
-        <v>2.1</v>
-      </c>
-      <c r="AW32">
-        <v>1.62</v>
-      </c>
-      <c r="AX32">
-        <v>1.35</v>
-      </c>
-      <c r="AY32">
-        <v>1.19</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>2.1</v>
-      </c>
-      <c r="BC32">
-        <v>1.91</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>203</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45756.79166666666</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45756</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="F33" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -6530,7 +4748,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L33">
         <v>2.46</v>
@@ -6605,87 +4823,33 @@
         <v>1.01</v>
       </c>
       <c r="AJ33" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AK33" t="s">
-        <v>222</v>
-      </c>
-      <c r="AL33">
-        <v>1.36</v>
-      </c>
-      <c r="AM33">
-        <v>1.4</v>
-      </c>
-      <c r="AN33">
-        <v>1.53</v>
-      </c>
-      <c r="AO33">
-        <v>11</v>
-      </c>
-      <c r="AP33">
-        <v>1.57</v>
-      </c>
-      <c r="AQ33">
-        <v>1.96</v>
-      </c>
-      <c r="AR33">
-        <v>2.55</v>
-      </c>
-      <c r="AS33">
-        <v>3.4</v>
-      </c>
-      <c r="AT33">
-        <v>4.6</v>
-      </c>
-      <c r="AU33">
-        <v>2.2</v>
-      </c>
-      <c r="AV33">
-        <v>1.73</v>
-      </c>
-      <c r="AW33">
-        <v>1.44</v>
-      </c>
-      <c r="AX33">
-        <v>1.26</v>
-      </c>
-      <c r="AY33">
-        <v>1.15</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>1.83</v>
-      </c>
-      <c r="BC33">
-        <v>2.38</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>204</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45756.79166666666</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45756</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C34" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="F34" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G34">
         <v>2</v>
@@ -6700,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L34">
         <v>2.14</v>
@@ -6775,87 +4939,33 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="AK34" t="s">
-        <v>223</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
-        <v>0</v>
-      </c>
-      <c r="AO34">
-        <v>9</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34">
-        <v>0</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
-      </c>
-      <c r="AW34">
-        <v>0</v>
-      </c>
-      <c r="AX34">
-        <v>0</v>
-      </c>
-      <c r="AY34">
-        <v>0</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>1.62</v>
-      </c>
-      <c r="BC34">
-        <v>2.2</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>205</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45756.83333333334</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45756</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="F35" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -6870,7 +4980,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L35">
         <v>2.15</v>
@@ -6945,87 +5055,33 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="AK35" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>0</v>
-      </c>
-      <c r="AN35">
-        <v>0</v>
-      </c>
-      <c r="AO35">
-        <v>10</v>
-      </c>
-      <c r="AP35">
-        <v>0</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>2</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35">
-        <v>0</v>
-      </c>
-      <c r="AV35">
-        <v>0</v>
-      </c>
-      <c r="AW35">
-        <v>0</v>
-      </c>
-      <c r="AX35">
-        <v>0</v>
-      </c>
-      <c r="AY35">
-        <v>0</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.73</v>
-      </c>
-      <c r="BC35">
-        <v>2.1</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45756.83333333334</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45756</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E36" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="F36" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -7040,7 +5096,7 @@
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L36">
         <v>2.05</v>
@@ -7115,87 +5171,33 @@
         <v>1.2</v>
       </c>
       <c r="AJ36" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="AK36" t="s">
-        <v>224</v>
-      </c>
-      <c r="AL36">
-        <v>1.18</v>
-      </c>
-      <c r="AM36">
-        <v>1.16</v>
-      </c>
-      <c r="AN36">
-        <v>1.47</v>
-      </c>
-      <c r="AO36">
-        <v>10</v>
-      </c>
-      <c r="AP36">
-        <v>0</v>
-      </c>
-      <c r="AQ36">
-        <v>0</v>
-      </c>
-      <c r="AR36">
-        <v>0</v>
-      </c>
-      <c r="AS36">
-        <v>0</v>
-      </c>
-      <c r="AT36">
-        <v>0</v>
-      </c>
-      <c r="AU36">
-        <v>0</v>
-      </c>
-      <c r="AV36">
-        <v>0</v>
-      </c>
-      <c r="AW36">
-        <v>0</v>
-      </c>
-      <c r="AX36">
-        <v>0</v>
-      </c>
-      <c r="AY36">
-        <v>0</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>1.77</v>
-      </c>
-      <c r="BC36">
-        <v>1.95</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>206</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45756.85416666666</v>
       </c>
     </row>
-    <row r="37" spans="1:56">
+    <row r="37" spans="1:38">
       <c r="A37" s="2">
         <v>45756</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="F37" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -7210,7 +5212,7 @@
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L37">
         <v>1.2</v>
@@ -7285,427 +5287,265 @@
         <v>1.13</v>
       </c>
       <c r="AJ37" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="AK37" t="s">
-        <v>225</v>
-      </c>
-      <c r="AL37">
-        <v>1.07</v>
-      </c>
-      <c r="AM37">
-        <v>1.15</v>
-      </c>
-      <c r="AN37">
-        <v>3.3</v>
-      </c>
-      <c r="AO37">
-        <v>14</v>
-      </c>
-      <c r="AP37">
-        <v>1.29</v>
-      </c>
-      <c r="AQ37">
-        <v>1.49</v>
-      </c>
-      <c r="AR37">
-        <v>1.79</v>
-      </c>
-      <c r="AS37">
-        <v>2.2</v>
-      </c>
-      <c r="AT37">
-        <v>2.8</v>
-      </c>
-      <c r="AU37">
-        <v>3.2</v>
-      </c>
-      <c r="AV37">
-        <v>2.4</v>
-      </c>
-      <c r="AW37">
-        <v>1.9</v>
-      </c>
-      <c r="AX37">
-        <v>1.57</v>
-      </c>
-      <c r="AY37">
-        <v>1.37</v>
-      </c>
-      <c r="AZ37">
-        <v>0</v>
-      </c>
-      <c r="BA37">
-        <v>0</v>
-      </c>
-      <c r="BB37">
-        <v>1.22</v>
-      </c>
-      <c r="BC37">
-        <v>4.5</v>
-      </c>
-      <c r="BD37" s="3">
+        <v>207</v>
+      </c>
+      <c r="AL37" s="3">
         <v>45756.89583333334</v>
       </c>
     </row>
-    <row r="38" spans="1:56">
+    <row r="38" spans="1:38">
       <c r="A38" s="2">
         <v>45756</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E38" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="F38" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L38">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="M38">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="N38">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="O38">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="P38">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="Q38">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="R38">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S38">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="T38">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="U38">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="W38">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X38">
         <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="Z38">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="AA38">
-        <v>3.95</v>
+        <v>7.1</v>
       </c>
       <c r="AB38">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="AC38">
-        <v>1.91</v>
+        <v>3.21</v>
       </c>
       <c r="AD38">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE38">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="AF38">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG38">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AH38">
-        <v>5.45</v>
+        <v>2.92</v>
       </c>
       <c r="AI38">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AJ38" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="AK38" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL38">
-        <v>1.04</v>
-      </c>
-      <c r="AM38">
-        <v>1.15</v>
-      </c>
-      <c r="AN38">
-        <v>4</v>
-      </c>
-      <c r="AO38">
-        <v>10</v>
-      </c>
-      <c r="AP38">
-        <v>1.41</v>
-      </c>
-      <c r="AQ38">
-        <v>1.67</v>
-      </c>
-      <c r="AR38">
-        <v>2.08</v>
-      </c>
-      <c r="AS38">
-        <v>2.65</v>
-      </c>
-      <c r="AT38">
-        <v>3.55</v>
-      </c>
-      <c r="AU38">
-        <v>2.65</v>
-      </c>
-      <c r="AV38">
-        <v>2.04</v>
-      </c>
-      <c r="AW38">
-        <v>1.65</v>
-      </c>
-      <c r="AX38">
-        <v>1.41</v>
-      </c>
-      <c r="AY38">
-        <v>1.24</v>
-      </c>
-      <c r="AZ38">
-        <v>0</v>
-      </c>
-      <c r="BA38">
-        <v>0</v>
-      </c>
-      <c r="BB38">
-        <v>1.17</v>
-      </c>
-      <c r="BC38">
-        <v>6</v>
-      </c>
-      <c r="BD38" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL38" s="3">
         <v>45756.89583333334</v>
       </c>
     </row>
-    <row r="39" spans="1:56">
+    <row r="39" spans="1:38">
       <c r="A39" s="2">
         <v>45756</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E39" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="F39" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" t="s">
+        <v>152</v>
+      </c>
+      <c r="L39">
+        <v>1.28</v>
+      </c>
+      <c r="M39">
+        <v>5.3</v>
+      </c>
+      <c r="N39">
+        <v>10</v>
+      </c>
+      <c r="O39">
+        <v>1.17</v>
+      </c>
+      <c r="P39">
+        <v>15</v>
+      </c>
+      <c r="Q39">
+        <v>6</v>
+      </c>
+      <c r="R39">
+        <v>1.36</v>
+      </c>
+      <c r="S39">
         <v>3</v>
       </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>2</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39" t="s">
-        <v>170</v>
-      </c>
-      <c r="L39">
-        <v>1.36</v>
-      </c>
-      <c r="M39">
-        <v>5.4</v>
-      </c>
-      <c r="N39">
-        <v>6.6</v>
-      </c>
-      <c r="O39">
-        <v>1.25</v>
-      </c>
-      <c r="P39">
-        <v>28</v>
-      </c>
-      <c r="Q39">
-        <v>3.75</v>
-      </c>
-      <c r="R39">
-        <v>1.2</v>
-      </c>
-      <c r="S39">
-        <v>4.33</v>
-      </c>
       <c r="T39">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="U39">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="V39">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="W39">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="Z39">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AA39">
-        <v>7.1</v>
+        <v>3.95</v>
       </c>
       <c r="AB39">
-        <v>1.32</v>
+        <v>1.83</v>
       </c>
       <c r="AC39">
-        <v>3.21</v>
+        <v>1.91</v>
       </c>
       <c r="AD39">
-        <v>1.87</v>
+        <v>2.83</v>
       </c>
       <c r="AE39">
-        <v>1.87</v>
+        <v>1.35</v>
       </c>
       <c r="AF39">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AG39">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AH39">
-        <v>2.92</v>
+        <v>5.45</v>
       </c>
       <c r="AI39">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AJ39" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="AK39" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL39">
-        <v>1.07</v>
-      </c>
-      <c r="AM39">
-        <v>1.15</v>
-      </c>
-      <c r="AN39">
-        <v>3.5</v>
-      </c>
-      <c r="AO39">
-        <v>12</v>
-      </c>
-      <c r="AP39">
-        <v>1.08</v>
-      </c>
-      <c r="AQ39">
-        <v>1.17</v>
-      </c>
-      <c r="AR39">
-        <v>1.3</v>
-      </c>
-      <c r="AS39">
-        <v>1.47</v>
-      </c>
-      <c r="AT39">
-        <v>1.73</v>
-      </c>
-      <c r="AU39">
-        <v>6.1</v>
-      </c>
-      <c r="AV39">
-        <v>4.3</v>
-      </c>
-      <c r="AW39">
-        <v>3.15</v>
-      </c>
-      <c r="AX39">
-        <v>2.43</v>
-      </c>
-      <c r="AY39">
-        <v>1.97</v>
-      </c>
-      <c r="AZ39">
-        <v>0</v>
-      </c>
-      <c r="BA39">
-        <v>0</v>
-      </c>
-      <c r="BB39">
-        <v>1.25</v>
-      </c>
-      <c r="BC39">
-        <v>3.75</v>
-      </c>
-      <c r="BD39" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL39" s="3">
         <v>45756.89583333334</v>
       </c>
     </row>
-    <row r="40" spans="1:56">
+    <row r="40" spans="1:38">
       <c r="A40" s="2">
         <v>45756</v>
       </c>
       <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" t="s">
         <v>72</v>
       </c>
-      <c r="C40" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" t="s">
-        <v>90</v>
-      </c>
       <c r="E40" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="F40" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -7720,7 +5560,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="L40">
         <v>1.2</v>
@@ -7795,66 +5635,12 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
       <c r="AK40" t="s">
-        <v>177</v>
-      </c>
-      <c r="AL40">
-        <v>0</v>
-      </c>
-      <c r="AM40">
-        <v>0</v>
-      </c>
-      <c r="AN40">
-        <v>0</v>
-      </c>
-      <c r="AO40">
-        <v>8</v>
-      </c>
-      <c r="AP40">
-        <v>0</v>
-      </c>
-      <c r="AQ40">
-        <v>0</v>
-      </c>
-      <c r="AR40">
-        <v>0</v>
-      </c>
-      <c r="AS40">
-        <v>0</v>
-      </c>
-      <c r="AT40">
-        <v>0</v>
-      </c>
-      <c r="AU40">
-        <v>0</v>
-      </c>
-      <c r="AV40">
-        <v>0</v>
-      </c>
-      <c r="AW40">
-        <v>0</v>
-      </c>
-      <c r="AX40">
-        <v>0</v>
-      </c>
-      <c r="AY40">
-        <v>0</v>
-      </c>
-      <c r="AZ40">
-        <v>0</v>
-      </c>
-      <c r="BA40">
-        <v>0</v>
-      </c>
-      <c r="BB40">
-        <v>1.2</v>
-      </c>
-      <c r="BC40">
-        <v>5.5</v>
-      </c>
-      <c r="BD40" s="3">
+        <v>160</v>
+      </c>
+      <c r="AL40" s="3">
         <v>45756.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-04-09.xlsx
+++ b/jogos_2025-04-09.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia Northern NSW NPL</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maitland</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>New Lambton</t>
+          <t>Yokohama F. Marinos</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="O2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['7', '66', '90+9']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['41', '89', '90+2']</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.15</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['1']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>['51']</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AI2" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45756.29166666666</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Australia Northern NSW NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Maitland</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Yokohama F. Marinos</t>
+          <t>New Lambton</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="O3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB3" t="n">
         <v>2.1</v>
       </c>
-      <c r="P3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AC3" t="n">
-        <v>1.57</v>
+        <v>1.31</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['7', '66', '90+9']</t>
+          <t>['1']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['41', '89', '90+2']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45756.29166666666</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1432,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>6</v>
+        <v>3.95</v>
       </c>
       <c r="O8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC8" t="n">
         <v>1.8</v>
       </c>
-      <c r="P8" t="n">
+      <c r="AD8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['45+4', '49', '53']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ8" t="n">
         <v>2.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['4', '9', '16']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>3.4</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45756.5</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.7</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>['4', '9', '16']</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.3</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['45+4', '49', '53']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45756.5</v>
@@ -1923,119 +1923,119 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Rīgas FS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M12" t="n">
+        <v>12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>14</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['28', '45']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
         <v>1</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M12" t="n">
+      <c r="AH12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>6</v>
-      </c>
-      <c r="N12" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X12" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>['24', '62']</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>['6']</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>4.33</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45756.54166666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y13" t="n">
         <v>2.2</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Z13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['17', '24', '30', '84', '90+4']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.5</v>
+        <v>2.11</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45756.54166666666</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,109 +2191,109 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5</v>
+      </c>
+      <c r="N14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="O14" t="n">
+      <c r="AD14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH14" t="n">
         <v>3.4</v>
       </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T14" t="n">
-        <v>3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['33', '41']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI14" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45756.54166666666</v>
@@ -2310,35 +2310,35 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rīgas FS</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['24', '62']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['6']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.07</v>
       </c>
-      <c r="M15" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" t="n">
-        <v>25</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>14</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X15" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['28', '45']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1</v>
-      </c>
       <c r="AH15" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AJ15" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45756.54166666666</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
       </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S16" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
         <v>1.32</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>['62']</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['17', '24', '30', '84', '90+4']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AI16" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45756.54166666666</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>7.8</v>
+        <v>2.35</v>
       </c>
       <c r="O17" t="n">
-        <v>1.68</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.49</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.2</v>
       </c>
-      <c r="S17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC17" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>['5']</t>
+          <t>['86']</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['33', '41']</t>
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.6</v>
+        <v>1.8</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45756.54166666666</v>
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>1860 München</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Sandhausen</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2722,7 +2722,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="N18" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="n">
         <v>2.75</v>
       </c>
-      <c r="T18" t="n">
-        <v>3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AB18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>['1', '12']</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AH18" t="n">
         <v>1.75</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>['39', '76']</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AI18" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45756.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Borussia Dortmund II</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.04</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="X19" t="n">
-        <v>2.92</v>
+        <v>4.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="AA19" t="n">
-        <v>3.58</v>
+        <v>2.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['12', '23', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['53']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45756.58333333334</v>
@@ -2965,22 +2965,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dynamo Dresden</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.72</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>4.38</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="R20" t="n">
         <v>1.3</v>
@@ -3015,59 +3015,59 @@
         <v>3.2</v>
       </c>
       <c r="T20" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
         <v>1.2</v>
       </c>
       <c r="X20" t="n">
-        <v>4.27</v>
+        <v>4.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['42', '73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['35', '48']</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45756.58333333334</v>
@@ -3094,25 +3094,25 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Dynamo Dresden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Borussia Dortmund II</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.6</v>
+        <v>4.38</v>
       </c>
       <c r="O21" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="R21" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>4.04</v>
+        <v>4.27</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="Z21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.15</v>
       </c>
-      <c r="AA21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '73']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['35', '48']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45756.58333333334</v>
@@ -3213,33 +3213,33 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="M22" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.36</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>['39', '76']</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
         <v>1.42</v>
       </c>
-      <c r="V22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>['50']</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45756.58333333334</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Ankaragücü</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.33</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="O23" t="n">
-        <v>2.55</v>
+        <v>2.79</v>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="V23" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X23" t="n">
-        <v>4.2</v>
+        <v>3.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>3.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.48</v>
+        <v>1.71</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.35</v>
+        <v>1.97</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['18', '35']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['3']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AG23" t="n">
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45756.58333333334</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,19 +3481,19 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1860 München</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sandhausen</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
@@ -3507,80 +3507,80 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="M24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.4</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="R24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U24" t="n">
         <v>1.33</v>
       </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.48</v>
-      </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="X24" t="n">
-        <v>4.17</v>
+        <v>2.92</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="Z24" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.75</v>
+        <v>3.58</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['1', '12']</t>
+          <t>['12', '23', '90+1']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AJ24" t="n">
         <v>2.35</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ankaragücü</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.27</v>
+        <v>2.39</v>
       </c>
       <c r="M25" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="N25" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="O25" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="P25" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.62</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="T25" t="n">
-        <v>2.84</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="V25" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X25" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['18', '35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45756.58333333334</v>
@@ -3997,25 +3997,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
         <v>3</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -4023,55 +4023,55 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.61</v>
+        <v>1.72</v>
       </c>
       <c r="M28" t="n">
-        <v>3.28</v>
+        <v>3.74</v>
       </c>
       <c r="N28" t="n">
-        <v>2.61</v>
+        <v>4.5</v>
       </c>
       <c r="O28" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="T28" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U28" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V28" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W28" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="X28" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA28" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC28" t="n">
         <v>2</v>
@@ -4081,25 +4081,25 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['62']</t>
+          <t>['4', '22', '35']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['7', '42', '90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.45</v>
+        <v>1.17</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.45</v>
+        <v>2.2</v>
       </c>
       <c r="AI28" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AJ28" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45756.65625</v>
@@ -4126,25 +4126,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
         <v>3</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -4152,55 +4152,55 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.72</v>
+        <v>2.61</v>
       </c>
       <c r="M29" t="n">
-        <v>3.74</v>
+        <v>3.28</v>
       </c>
       <c r="N29" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA29" t="n">
         <v>4.5</v>
       </c>
-      <c r="O29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AB29" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AC29" t="n">
         <v>2</v>
@@ -4210,25 +4210,25 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>['4', '22', '35']</t>
+          <t>['62']</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['7', '42', '90+1']</t>
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.2</v>
+        <v>1.45</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45756.65625</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,22 +4255,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FC Barcelona</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -4281,65 +4281,65 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="M30" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="N30" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="O30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.83</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X30" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD30" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>['25', '48', '66', '77']</t>
+          <t>['90+4']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4348,16 +4348,16 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.95</v>
+        <v>2.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45756.66666666666</v>
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>FC Barcelona</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,43 +4410,43 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="N31" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="O31" t="n">
         <v>1.83</v>
       </c>
       <c r="P31" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="U31" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="V31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>4.9</v>
+        <v>5.95</v>
       </c>
       <c r="Y31" t="n">
         <v>1.67</v>
@@ -4455,38 +4455,38 @@
         <v>2.1</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.01</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>['39', '49', '90+2']</t>
+          <t>['25', '48', '66', '77']</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG31" t="n">
         <v>1.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="AI31" t="n">
         <v>1.29</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45756.66666666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="M32" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>7.3</v>
       </c>
       <c r="O32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.25</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W32" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="X32" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="Z32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD32" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['90+4']</t>
+          <t>['39', '49', '90+2']</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45756.66666666666</v>
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vélez Sarsfield</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4797,83 +4797,83 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>2.85</v>
+        <v>3.29</v>
       </c>
       <c r="N34" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="O34" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>['64']</t>
+        </is>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ34" t="n">
         <v>1.91</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>4</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>4</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['25', '49', '56', '90+3']</t>
-        </is>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>2.38</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45756.79166666666</v>
@@ -4900,109 +4900,109 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Vélez Sarsfield</t>
         </is>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="M35" t="n">
-        <v>3.29</v>
+        <v>2.85</v>
       </c>
       <c r="N35" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="O35" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.5</v>
       </c>
-      <c r="S35" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X35" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="Y35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC35" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AD35" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>['25', '49', '56', '90+3']</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH35" t="n">
         <v>1.53</v>
       </c>
-      <c r="AA35" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['64']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AI35" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45756.79166666666</v>
@@ -5545,22 +5545,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cerro Porteño</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -5571,65 +5571,65 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="M40" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="N40" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="O40" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="P40" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="R40" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S40" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="T40" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="V40" t="n">
         <v>1.01</v>
       </c>
       <c r="W40" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="X40" t="n">
-        <v>3.95</v>
+        <v>7.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.83</v>
+        <v>1.32</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.91</v>
+        <v>3.21</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.83</v>
+        <v>1.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['12', '44', '58']</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5638,16 +5638,16 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AH40" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AJ40" t="n">
-        <v>6</v>
+        <v>3.75</v>
       </c>
       <c r="AK40" s="3" t="n">
         <v>45756.89583333334</v>
@@ -5674,109 +5674,109 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Cerro Porteño</t>
         </is>
       </c>
       <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M41" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="N41" t="n">
+        <v>10</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>11</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S41" t="n">
         <v>3</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M41" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="N41" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P41" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>7</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S41" t="n">
-        <v>4.33</v>
-      </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>2.63</v>
       </c>
       <c r="U41" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="V41" t="n">
         <v>1.01</v>
       </c>
       <c r="W41" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.04</v>
       </c>
-      <c r="X41" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['12', '44', '58']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AH41" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45756.89583333334</v>
